--- a/reviews/a-envoyer/otea-filmakers-2026-09-21.xlsx
+++ b/reviews/a-envoyer/otea-filmakers-2026-09-21.xlsx
@@ -885,7 +885,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-18T06:05:18</t>
+          <t>2026-09-18T09:30:43</t>
         </is>
       </c>
     </row>
